--- a/src/puck/dotpipeline/best60combos.xlsx
+++ b/src/puck/dotpipeline/best60combos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jdreiling/Desktop/puck/puck/src/puck/dotpipeline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{335106F2-A55F-F04C-A35D-0EEE7A77B6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B9BD74B-C118-6345-8231-47BE43FFA761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3080" yWindow="2200" windowWidth="28040" windowHeight="17180" xr2:uid="{675974BE-1FEA-CD42-824C-41B6BA111F52}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="90">
   <si>
     <t>(11, 350, np.float64(0.8))</t>
   </si>
@@ -266,6 +266,30 @@
   </si>
   <si>
     <t>(1, 400, np.float64(0.8))</t>
+  </si>
+  <si>
+    <t>.8 and .7 seems to do very well</t>
+  </si>
+  <si>
+    <t>anywhere in the 300 to 400 range works, but we know for a fact 400 reduces the upper spread</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>In the improved version, a value greater than 3 tends to do well</t>
+  </si>
+  <si>
+    <t>.7 .75 .8</t>
+  </si>
+  <si>
+    <t>400 - 500</t>
+  </si>
+  <si>
+    <t>5 15</t>
+  </si>
+  <si>
+    <t>Curious to see how many of the new ones have a close enough score?</t>
   </si>
 </sst>
 </file>
@@ -408,7 +432,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -586,6 +610,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -749,8 +779,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1126,248 +1157,292 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3CF57C6-B84D-6B49-AFAD-D98CF315F9C5}">
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="20.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B1">
         <v>0</v>
       </c>
       <c r="C1">
         <v>1</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H2" s="1"/>
+      <c r="K2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H3" s="1"/>
+      <c r="K3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H4" s="1"/>
+      <c r="K4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H5" s="1"/>
+      <c r="K5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="C7" t="s">
         <v>0</v>
       </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="K7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="C8" t="s">
         <v>2</v>
       </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="K8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
       </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="K9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="C10" t="s">
         <v>6</v>
       </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
       </c>
-      <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="1"/>
+      <c r="K11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
       </c>
-      <c r="F12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="C13" t="s">
         <v>17</v>
       </c>
-      <c r="F13" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="C14" t="s">
         <v>19</v>
       </c>
-      <c r="F14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="C15" t="s">
         <v>21</v>
       </c>
-      <c r="F15" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
       </c>
-      <c r="F16" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="C17" t="s">
         <v>24</v>
       </c>
-      <c r="F17" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1377,14 +1452,15 @@
       <c r="C18" t="s">
         <v>12</v>
       </c>
-      <c r="F18" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1394,14 +1470,15 @@
       <c r="C19" t="s">
         <v>27</v>
       </c>
-      <c r="F19" t="s">
-        <v>28</v>
-      </c>
-      <c r="G19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1411,14 +1488,15 @@
       <c r="C20" t="s">
         <v>13</v>
       </c>
-      <c r="F20" t="s">
-        <v>29</v>
-      </c>
-      <c r="G20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1428,14 +1506,15 @@
       <c r="C21" t="s">
         <v>14</v>
       </c>
-      <c r="F21" t="s">
-        <v>30</v>
-      </c>
-      <c r="G21" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1445,14 +1524,15 @@
       <c r="C22" t="s">
         <v>15</v>
       </c>
-      <c r="F22" t="s">
-        <v>31</v>
-      </c>
-      <c r="G22" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1462,14 +1542,15 @@
       <c r="C23" t="s">
         <v>16</v>
       </c>
-      <c r="F23" t="s">
-        <v>32</v>
-      </c>
-      <c r="G23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1479,14 +1560,15 @@
       <c r="C24" t="s">
         <v>18</v>
       </c>
-      <c r="F24" t="s">
-        <v>34</v>
-      </c>
-      <c r="G24" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1496,14 +1578,15 @@
       <c r="C25" t="s">
         <v>20</v>
       </c>
-      <c r="F25" t="s">
-        <v>36</v>
-      </c>
-      <c r="G25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1513,14 +1596,15 @@
       <c r="C26" t="s">
         <v>22</v>
       </c>
-      <c r="F26" t="s">
-        <v>38</v>
-      </c>
-      <c r="G26" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1530,14 +1614,15 @@
       <c r="C27" t="s">
         <v>23</v>
       </c>
-      <c r="F27" t="s">
-        <v>40</v>
-      </c>
-      <c r="G27" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1547,14 +1632,15 @@
       <c r="C28" t="s">
         <v>25</v>
       </c>
-      <c r="F28" t="s">
-        <v>41</v>
-      </c>
-      <c r="G28" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H28" s="1"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1564,14 +1650,15 @@
       <c r="C29" t="s">
         <v>26</v>
       </c>
-      <c r="F29" t="s">
-        <v>42</v>
-      </c>
-      <c r="G29" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F29" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1581,14 +1668,15 @@
       <c r="C30" t="s">
         <v>28</v>
       </c>
-      <c r="F30" t="s">
-        <v>43</v>
-      </c>
-      <c r="G30" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1598,14 +1686,15 @@
       <c r="C31" t="s">
         <v>29</v>
       </c>
-      <c r="F31" t="s">
-        <v>44</v>
-      </c>
-      <c r="G31" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F31" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>30</v>
       </c>
@@ -1615,14 +1704,15 @@
       <c r="C32" t="s">
         <v>30</v>
       </c>
-      <c r="F32" t="s">
-        <v>45</v>
-      </c>
-      <c r="G32" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F32" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>31</v>
       </c>
@@ -1632,14 +1722,15 @@
       <c r="C33" t="s">
         <v>31</v>
       </c>
-      <c r="F33" t="s">
-        <v>46</v>
-      </c>
-      <c r="G33" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F33" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>32</v>
       </c>
@@ -1649,14 +1740,15 @@
       <c r="C34" t="s">
         <v>32</v>
       </c>
-      <c r="F34" t="s">
-        <v>47</v>
-      </c>
-      <c r="G34" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>33</v>
       </c>
@@ -1666,14 +1758,15 @@
       <c r="C35" t="s">
         <v>34</v>
       </c>
-      <c r="F35" t="s">
-        <v>48</v>
-      </c>
-      <c r="G35" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F35" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>34</v>
       </c>
@@ -1683,14 +1776,15 @@
       <c r="C36" t="s">
         <v>36</v>
       </c>
-      <c r="F36" t="s">
-        <v>49</v>
-      </c>
-      <c r="G36" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F36" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1700,14 +1794,15 @@
       <c r="C37" t="s">
         <v>38</v>
       </c>
-      <c r="F37" t="s">
-        <v>50</v>
-      </c>
-      <c r="G37" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F37" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1717,14 +1812,15 @@
       <c r="C38" t="s">
         <v>40</v>
       </c>
-      <c r="F38" t="s">
-        <v>33</v>
-      </c>
-      <c r="G38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F38" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H38" s="1"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>37</v>
       </c>
@@ -1735,13 +1831,13 @@
         <v>41</v>
       </c>
       <c r="F39" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G39" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1752,13 +1848,13 @@
         <v>42</v>
       </c>
       <c r="F40" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G40" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>39</v>
       </c>
@@ -1769,13 +1865,13 @@
         <v>43</v>
       </c>
       <c r="F41" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G41" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>40</v>
       </c>
@@ -1786,13 +1882,13 @@
         <v>44</v>
       </c>
       <c r="F42" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="G42" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>41</v>
       </c>
@@ -1806,10 +1902,10 @@
         <v>51</v>
       </c>
       <c r="G43" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>42</v>
       </c>
@@ -1823,10 +1919,10 @@
         <v>52</v>
       </c>
       <c r="G44" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>43</v>
       </c>
@@ -1843,7 +1939,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>44</v>
       </c>
@@ -1860,7 +1956,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>45</v>
       </c>
@@ -1877,7 +1973,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>46</v>
       </c>
